--- a/services/message_detector/uploads/ScamSense_Single_Test_Message.xlsx
+++ b/services/message_detector/uploads/ScamSense_Single_Test_Message.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chunk\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/805603baaeaf2077/Desktop/Message_Scan_Detector_Test_Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{B385EB35-DADF-441E-950D-4FF512BAEEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DEF5883B-E06E-4F7B-A447-15D14FE468E7}"/>
+    <workbookView minimized="1" xWindow="12040" yWindow="5620" windowWidth="7500" windowHeight="6000" xr2:uid="{DEF5883B-E06E-4F7B-A447-15D14FE468E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
